--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488296_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488296_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.1222</v>
+        <v>9.6172</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7433</v>
+        <v>5.6569</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3789</v>
+        <v>3.9603</v>
       </c>
       <c r="G2" t="n">
         <v>4.4876</v>
@@ -610,13 +610,13 @@
         <v>2.594</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3375</v>
+        <v>0.8325</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3631</v>
+        <v>0.2767</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9744</v>
+        <v>0.5558</v>
       </c>
       <c r="V2" t="n">
         <v>1.8883</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8999</v>
+        <v>2.9283</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.3736</v>
+        <v>-0.0251</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2735</v>
+        <v>2.9534</v>
       </c>
       <c r="G3" t="n">
         <v>1.6148</v>
@@ -688,13 +688,13 @@
         <v>1.297</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.012</v>
+        <v>0.0165</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7113</v>
+        <v>-0.3628</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6993</v>
+        <v>0.3793</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. SAENZ - DIAZ MURO</t>
+          <t>M. CABEZA RUEDA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4531</v>
+        <v>1.7403</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7804</v>
+        <v>-0.4469</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6728</v>
+        <v>2.1872</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4641</v>
+        <v>1.5792</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1323</v>
+        <v>1.1937</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3318</v>
+        <v>0.3856</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.0526</v>
+        <v>0.8096</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5066000000000001</v>
+        <v>0.7468</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5592</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5167</v>
+        <v>0.7696</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3743</v>
+        <v>0.4469</v>
       </c>
       <c r="O5" t="n">
-        <v>0.891</v>
+        <v>0.3227</v>
       </c>
       <c r="P5" t="n">
-        <v>1.4823</v>
+        <v>0.3706</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1853</v>
+        <v>-0.9264</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6676</v>
+        <v>1.297</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4512</v>
+        <v>-0.2095</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7039</v>
+        <v>-0.3301</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2527</v>
+        <v>0.1206</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9444</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. REMESAL LEON</t>
+          <t>M. EZOMO GERVILLA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2115</v>
+        <v>1.5826</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.338</v>
+        <v>1.5069</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5495</v>
+        <v>0.0757</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2663</v>
+        <v>1.3722</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7408</v>
+        <v>1.727</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.4745</v>
+        <v>-0.3548</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2158</v>
+        <v>2.8509</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9671</v>
+        <v>2.8295</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.7512</v>
+        <v>0.0214</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0505</v>
+        <v>-1.4787</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2263</v>
+        <v>-1.1026</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2767</v>
+        <v>-0.3761</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.8529</v>
+        <v>0.3706</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.891</v>
+        <v>-1.1117</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0382</v>
+        <v>1.4823</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2258</v>
+        <v>0.1548</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.235</v>
+        <v>0.0827</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4608</v>
+        <v>0.0721</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5722</v>
+        <v>-0.315</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5722</v>
+        <v>-0.315</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. CABEZA RUEDA</t>
+          <t>D. CASTRO DIANEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1696</v>
+        <v>1.3481</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6975</v>
+        <v>1.9712</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8671</v>
+        <v>-0.6231</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5792</v>
+        <v>1.768</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1937</v>
+        <v>1.2059</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3856</v>
+        <v>0.5621</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8096</v>
+        <v>2.8697</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7468</v>
+        <v>2.2156</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.6541</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7696</v>
+        <v>-1.1017</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4469</v>
+        <v>-1.0097</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3227</v>
+        <v>-0.092</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3706</v>
+        <v>0.1853</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9264</v>
+        <v>-1.1117</v>
       </c>
       <c r="R7" t="n">
         <v>1.297</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7802</v>
+        <v>0.0242</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5807</v>
+        <v>0.2133</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1995</v>
+        <v>-0.189</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.6294</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. EZOMO GERVILLA</t>
+          <t>J. REMESAL LEON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8117</v>
+        <v>1.3444</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8099</v>
+        <v>-1.0327</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0019</v>
+        <v>2.3771</v>
       </c>
       <c r="G8" t="n">
-        <v>1.3722</v>
+        <v>1.2663</v>
       </c>
       <c r="H8" t="n">
-        <v>1.727</v>
+        <v>2.7408</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3548</v>
+        <v>-1.4745</v>
       </c>
       <c r="J8" t="n">
-        <v>2.8509</v>
+        <v>1.2158</v>
       </c>
       <c r="K8" t="n">
-        <v>2.8295</v>
+        <v>2.9671</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0214</v>
+        <v>-1.7512</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4787</v>
+        <v>0.0505</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1026</v>
+        <v>-0.2263</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3761</v>
+        <v>0.2767</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3706</v>
+        <v>-1.8529</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1117</v>
+        <v>-3.891</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4823</v>
+        <v>2.0382</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.616</v>
+        <v>0.3588</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6143</v>
+        <v>0.0703</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0018</v>
+        <v>0.2885</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.315</v>
+        <v>1.5722</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.315</v>
+        <v>1.5722</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. CASTRO DIANEZ</t>
+          <t>C. SAENZ - DIAZ MURO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.772</v>
+        <v>0.8956</v>
       </c>
       <c r="E9" t="n">
-        <v>1.666</v>
+        <v>0.2475</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.894</v>
+        <v>0.6481</v>
       </c>
       <c r="G9" t="n">
-        <v>1.768</v>
+        <v>0.4641</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2059</v>
+        <v>0.1323</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5621</v>
+        <v>0.3318</v>
       </c>
       <c r="J9" t="n">
-        <v>2.8697</v>
+        <v>-0.0526</v>
       </c>
       <c r="K9" t="n">
-        <v>2.2156</v>
+        <v>0.5066000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6541</v>
+        <v>-0.5592</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1017</v>
+        <v>0.5167</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0097</v>
+        <v>-0.3743</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.092</v>
+        <v>0.891</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1853</v>
+        <v>1.4823</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1117</v>
+        <v>-0.1853</v>
       </c>
       <c r="R9" t="n">
-        <v>1.297</v>
+        <v>1.6676</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5518999999999999</v>
+        <v>-0.1063</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.092</v>
+        <v>0.171</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4599</v>
+        <v>-0.2773</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6294</v>
+        <v>-0.9444</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6294</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. ESCAMILLA DE SANTOS</t>
+          <t>M. TRILLO MANGANO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.505</v>
+        <v>0.4896</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2634</v>
+        <v>-0.9844000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7684</v>
+        <v>1.474</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1917</v>
+        <v>0.8928</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0319</v>
+        <v>0.1985</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1597</v>
+        <v>0.6943</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7236</v>
+        <v>0.0629</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7864</v>
+        <v>0.0215</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.0415</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5319</v>
+        <v>0.8299</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7544</v>
+        <v>0.177</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2226</v>
+        <v>0.6529</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9264</v>
+        <v>0.7411</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3823</v>
+        <v>-0.2179</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0721</v>
+        <v>-0.1209</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3101</v>
+        <v>-0.097</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. TRILLO MANGANO</t>
+          <t>D. ESCAMILLA DE SANTOS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2932</v>
+        <v>0.3152</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0824</v>
+        <v>-1.5025</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3755</v>
+        <v>1.8177</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8928</v>
+        <v>-0.1917</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1985</v>
+        <v>-0.0319</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6943</v>
+        <v>-0.1597</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0629</v>
+        <v>-0.7236</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0215</v>
+        <v>-0.7864</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0415</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>0.8299</v>
+        <v>0.5319</v>
       </c>
       <c r="N11" t="n">
-        <v>0.177</v>
+        <v>0.7544</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6529</v>
+        <v>-0.2226</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1853</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7411</v>
+        <v>0.9264</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4143</v>
+        <v>0.1924</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2189</v>
+        <v>-0.1669</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1955</v>
+        <v>0.3594</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0987</v>
+        <v>-0.1398</v>
       </c>
       <c r="E12" t="n">
-        <v>0.799</v>
+        <v>0.462</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7003</v>
+        <v>-0.6018</v>
       </c>
       <c r="G12" t="n">
         <v>-0.5863</v>
@@ -1390,13 +1390,13 @@
         <v>0.1853</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4997</v>
+        <v>0.2611</v>
       </c>
       <c r="T12" t="n">
-        <v>0.434</v>
+        <v>0.097</v>
       </c>
       <c r="U12" t="n">
-        <v>0.06569999999999999</v>
+        <v>0.1641</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ - GUERRA SALGUEIRO</t>
+          <t>C. GALAN PLAZA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.4721</v>
+        <v>-1.4711</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.4466</v>
+        <v>-0.7523</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0256</v>
+        <v>-0.7187</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.1191</v>
+        <v>-1.5827</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.789</v>
+        <v>-1.145</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3301</v>
+        <v>-0.4377</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.8083</v>
+        <v>-0.6314</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.8083</v>
+        <v>-0.6314</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.3108</v>
+        <v>-0.9513</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9807</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3301</v>
+        <v>-0.4377</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.3706</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3151</v>
+        <v>0.1116</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4004</v>
+        <v>-0.1209</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0853</v>
+        <v>0.2325</v>
       </c>
       <c r="V13" t="n">
-        <v>1.8877</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.8877</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. GALAN PLAZA</t>
+          <t>J. RODRIGUEZ - GUERRA SALGUEIRO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.5991</v>
+        <v>-1.564</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.905</v>
+        <v>-0.5877</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6941000000000001</v>
+        <v>-0.9762999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.5827</v>
+        <v>-3.1191</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.145</v>
+        <v>-2.789</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4377</v>
+        <v>-0.3301</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.6314</v>
+        <v>-1.8083</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.6314</v>
+        <v>-1.8083</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9513</v>
+        <v>-1.3108</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5135999999999999</v>
+        <v>-0.9807</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4377</v>
+        <v>-0.3301</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0164</v>
+        <v>0.2232</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2736</v>
+        <v>0.2593</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2572</v>
+        <v>-0.0361</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.8877</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.8877</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>18.776</v>
+        <v>19.5967</v>
       </c>
       <c r="E15" t="n">
-        <v>6.2024</v>
+        <v>7.023199999999999</v>
       </c>
       <c r="F15" t="n">
         <v>12.5736</v>
@@ -1612,10 +1612,10 @@
         <v>-2.8143</v>
       </c>
       <c r="O15" t="n">
-        <v>1.806500000000001</v>
+        <v>1.8065</v>
       </c>
       <c r="P15" t="n">
-        <v>3.705700000000001</v>
+        <v>3.7057</v>
       </c>
       <c r="Q15" t="n">
         <v>-10.1906</v>
@@ -1624,13 +1624,13 @@
         <v>13.8965</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8208</v>
+        <v>1.6414</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7523</v>
+        <v>0.06869999999999998</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5728</v>
+        <v>1.5729</v>
       </c>
       <c r="V15" t="n">
         <v>3.7738</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.5208</v>
+        <v>4.2431</v>
       </c>
       <c r="E16" t="n">
-        <v>4.6203</v>
+        <v>4.1307</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.09950000000000001</v>
+        <v>0.1124</v>
       </c>
       <c r="G16" t="n">
         <v>2.4755</v>
@@ -1702,13 +1702,13 @@
         <v>1.1117</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4895</v>
+        <v>0.2117</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6914</v>
+        <v>0.2018</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.202</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>0.6294</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5587</v>
+        <v>0.0878</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4018</v>
+        <v>0.5976</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9604</v>
+        <v>-0.5098</v>
       </c>
       <c r="G17" t="n">
         <v>-1.6355</v>
@@ -1780,13 +1780,13 @@
         <v>0.7411</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9232</v>
+        <v>-0.2767</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.669</v>
+        <v>-0.4731</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2542</v>
+        <v>0.1965</v>
       </c>
       <c r="V17" t="n">
         <v>1.2589</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6541</v>
+        <v>-0.7296</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4272</v>
+        <v>-0.1334</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2269</v>
+        <v>-0.5962</v>
       </c>
       <c r="G18" t="n">
         <v>-2.012</v>
@@ -1858,13 +1858,13 @@
         <v>1.297</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0609</v>
+        <v>-0.0146</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.669</v>
+        <v>-0.3752</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7299</v>
+        <v>0.3606</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3127</v>
+        <v>-1.0665</v>
       </c>
       <c r="E19" t="n">
         <v>0.5637</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8765</v>
+        <v>-1.6303</v>
       </c>
       <c r="G19" t="n">
         <v>-0.3517</v>
@@ -1936,13 +1936,13 @@
         <v>1.297</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3071</v>
+        <v>-0.0609</v>
       </c>
       <c r="T19" t="n">
         <v>-0.0037</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3034</v>
+        <v>-0.0572</v>
       </c>
       <c r="V19" t="n">
         <v>-1.9509</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7433</v>
+        <v>-1.5234</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7364</v>
+        <v>-1.4426</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0069</v>
+        <v>-0.0808</v>
       </c>
       <c r="G20" t="n">
         <v>-1.7823</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2243</v>
+        <v>0.4443</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3283</v>
+        <v>-0.0345</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5526</v>
+        <v>0.4788</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3814</v>
+        <v>-2.3476</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.133</v>
+        <v>-1.4268</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2484</v>
+        <v>-0.9208</v>
       </c>
       <c r="G21" t="n">
         <v>-0.3008</v>
@@ -2092,13 +2092,13 @@
         <v>0.7411</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.34</v>
+        <v>-0.3062</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2027</v>
+        <v>-0.0911</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5427</v>
+        <v>-0.2151</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6289</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. CAMPOS CAMPOS</t>
+          <t>M. ORTEGA CARO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6441</v>
+        <v>-2.6301</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9792</v>
+        <v>-2.8448</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3352</v>
+        <v>0.2147</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.3217</v>
+        <v>-3.4991</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8838</v>
+        <v>-0.748</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.4379</v>
+        <v>-2.7511</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9038</v>
+        <v>-2.6875</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.2107</v>
+        <v>-0.8119</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6931</v>
+        <v>-1.8756</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.418</v>
+        <v>-0.8115</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6731</v>
+        <v>0.0639</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7448</v>
+        <v>-0.8754</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9264</v>
+        <v>1.1117</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.8529</v>
+        <v>-0.1853</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9264</v>
+        <v>1.297</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0368</v>
+        <v>0.1349</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2226</v>
+        <v>0.028</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2594</v>
+        <v>0.1069</v>
       </c>
       <c r="V22" t="n">
-        <v>0.5673</v>
+        <v>-0.3777</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.5673</v>
+        <v>-0.3777</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. TEJADA CAMACHO</t>
+          <t>J. CAMPOS CAMPOS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1115</v>
+        <v>-2.766</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.8244</v>
+        <v>-3.1751</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7129</v>
+        <v>0.409</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1559</v>
+        <v>-2.3217</v>
       </c>
       <c r="H23" t="n">
-        <v>1.8425</v>
+        <v>-0.8838</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.9984</v>
+        <v>-1.4379</v>
       </c>
       <c r="J23" t="n">
-        <v>0.5628</v>
+        <v>-0.9038</v>
       </c>
       <c r="K23" t="n">
-        <v>1.8163</v>
+        <v>-0.2107</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.2536</v>
+        <v>-0.6931</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.7187</v>
+        <v>-1.418</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0262</v>
+        <v>-0.6731</v>
       </c>
       <c r="O23" t="n">
         <v>-0.7448</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.5205</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.8175</v>
+        <v>-1.8529</v>
       </c>
       <c r="R23" t="n">
-        <v>1.297</v>
+        <v>0.9264</v>
       </c>
       <c r="S23" t="n">
-        <v>1.257</v>
+        <v>-0.0852</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4303</v>
+        <v>-0.4184</v>
       </c>
       <c r="U23" t="n">
-        <v>0.8267</v>
+        <v>0.3333</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6921</v>
+        <v>0.5673</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.6921</v>
+        <v>0.5673</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. ORTEGA CARO</t>
+          <t>A. RODRIGUEZ LOPEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.3012</v>
+        <v>-3.2304</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.0407</v>
+        <v>-2.3262</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2605</v>
+        <v>-0.9042</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.4991</v>
+        <v>-2.4117</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.748</v>
+        <v>-1.5285</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.7511</v>
+        <v>-0.8832</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.6875</v>
+        <v>-0.9266</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.8119</v>
+        <v>0.1718</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.8756</v>
+        <v>-1.0984</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.8115</v>
+        <v>-1.4851</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0639</v>
+        <v>-1.7003</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.8754</v>
+        <v>0.2152</v>
       </c>
       <c r="P24" t="n">
-        <v>1.1117</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.1853</v>
+        <v>-0.9264</v>
       </c>
       <c r="R24" t="n">
-        <v>1.297</v>
+        <v>0.7411</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5362</v>
+        <v>-0.319</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1679</v>
+        <v>-0.4731</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3683</v>
+        <v>0.1542</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.3777</v>
+        <v>-0.3144</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.3777</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ LOPEZ</t>
+          <t>J. MORALES ZARCO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.483</v>
+        <v>-3.7232</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.522</v>
+        <v>-2.3986</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.9609</v>
+        <v>-1.3246</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.4117</v>
+        <v>1.5195</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.5285</v>
+        <v>1.7252</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.8832</v>
+        <v>-0.2057</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.9266</v>
+        <v>1.5623</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1718</v>
+        <v>1.4379</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.0984</v>
+        <v>0.1244</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.4851</v>
+        <v>-0.0428</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.7003</v>
+        <v>0.2873</v>
       </c>
       <c r="O25" t="n">
-        <v>0.2152</v>
+        <v>-0.3301</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.1853</v>
+        <v>-3.1499</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.9264</v>
+        <v>-3.891</v>
       </c>
       <c r="R25" t="n">
         <v>0.7411</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5715</v>
+        <v>0.1725</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.669</v>
+        <v>-0.0699</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0975</v>
+        <v>0.2425</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.3144</v>
+        <v>-2.2654</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.3144</v>
+        <v>-2.2654</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>J. MORALES ZARCO</t>
+          <t>A. TEJADA CAMACHO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.1069</v>
+        <v>-3.7843</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.4966</v>
+        <v>-4.1182</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.6104</v>
+        <v>0.3339</v>
       </c>
       <c r="G26" t="n">
-        <v>1.5195</v>
+        <v>-0.1559</v>
       </c>
       <c r="H26" t="n">
-        <v>1.7252</v>
+        <v>1.8425</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2057</v>
+        <v>-1.9984</v>
       </c>
       <c r="J26" t="n">
-        <v>1.5623</v>
+        <v>0.5628</v>
       </c>
       <c r="K26" t="n">
-        <v>1.4379</v>
+        <v>1.8163</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1244</v>
+        <v>-1.2536</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.0428</v>
+        <v>-0.7187</v>
       </c>
       <c r="N26" t="n">
-        <v>0.2873</v>
+        <v>0.0262</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.3301</v>
+        <v>-0.7448</v>
       </c>
       <c r="P26" t="n">
-        <v>-3.1499</v>
+        <v>-3.5205</v>
       </c>
       <c r="Q26" t="n">
-        <v>-3.891</v>
+        <v>-4.8175</v>
       </c>
       <c r="R26" t="n">
-        <v>0.7411</v>
+        <v>1.297</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.2112</v>
+        <v>0.5841</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1679</v>
+        <v>0.1365</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.0433</v>
+        <v>0.4476</v>
       </c>
       <c r="V26" t="n">
-        <v>-2.2654</v>
+        <v>-0.6921</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-2.2654</v>
+        <v>-0.6921</v>
       </c>
     </row>
     <row r="27">
@@ -2515,19 +2515,19 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-18.7761</v>
+        <v>-17.4702</v>
       </c>
       <c r="E27" t="n">
         <v>-12.5737</v>
       </c>
       <c r="F27" t="n">
-        <v>-6.2023</v>
+        <v>-4.8967</v>
       </c>
       <c r="G27" t="n">
         <v>-10.4757</v>
       </c>
       <c r="H27" t="n">
-        <v>-5.3678</v>
+        <v>-5.367799999999999</v>
       </c>
       <c r="I27" t="n">
         <v>-5.107699999999999</v>
@@ -2545,13 +2545,13 @@
         <v>-11.4833</v>
       </c>
       <c r="N27" t="n">
-        <v>-8.181899999999999</v>
+        <v>-8.181900000000001</v>
       </c>
       <c r="O27" t="n">
         <v>-3.3011</v>
       </c>
       <c r="P27" t="n">
-        <v>-3.705900000000001</v>
+        <v>-3.7059</v>
       </c>
       <c r="Q27" t="n">
         <v>-13.8966</v>
@@ -2560,13 +2560,13 @@
         <v>10.1905</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.8207000000000002</v>
+        <v>0.4848999999999999</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.573</v>
+        <v>-1.5727</v>
       </c>
       <c r="U27" t="n">
-        <v>0.7522</v>
+        <v>2.058</v>
       </c>
       <c r="V27" t="n">
         <v>-3.7738</v>
